--- a/examples/branch_reports/集团总册.xlsx
+++ b/examples/branch_reports/集团总册.xlsx
@@ -18,6 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分公司×部门×职级" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-摘要" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分公司对比" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分公司趋势对比" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常数据汇总" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,7 +591,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E:\trae-bz\TraeProjects\1294\examples\合并花名册.xlsx</t>
+          <t>E:\trae-bz\TraeProjects\1294\examples\集团花名册_Q2.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -876,6 +878,1158 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>分公司</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>上海总部</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>上海总部</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>上海总部</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>上海总部</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>上海总部</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>上海总部</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>北京分公司</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>上海总部</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>广州分公司</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>深圳分公司</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>入职</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>异常类型</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>异常值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>出现次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>员工编号重复</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>员工编号</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SH00005</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>310101198102020012</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>310101198203030025</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>310101198304040038</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>310101198405050040</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>310101198607070066</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>310101198708080079</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>310101198809090081</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>310101198910100096</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>310101199011110105</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>310101199112120118</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>310101199201130123</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>310101199302140136</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>310101199403150149</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>31010119800101000X</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>身份证号重复</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>310101198506060053</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>必填字段为空</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>(空值 1 条)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
